--- a/output/graficos_dimensiones/comunal_e_preneta_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_preneta_a_2021_valparaiso.xlsx
@@ -135,18 +135,18 @@
     <t xml:space="preserve">Algarrobo</t>
   </si>
   <si>
+    <t xml:space="preserve">Santa María</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llaillay</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rinconada</t>
   </si>
   <si>
-    <t xml:space="preserve">Llaillay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa María</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Esteban</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:50</t>
+    <t xml:space="preserve">2026-09-09 23:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1164,7 +1164,7 @@
         <v>39</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>5303</v>
+        <v>5706</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -1177,7 +1177,7 @@
         <v>40</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>5703</v>
+        <v>5304</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -1190,7 +1190,7 @@
         <v>41</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>5706</v>
+        <v>5703</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -1203,7 +1203,7 @@
         <v>42</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>5304</v>
+        <v>5303</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_preneta_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_preneta_a_2021_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:50</t>
+    <t xml:space="preserve">2026-09-18 10:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
